--- a/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
+++ b/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5E6056-E769-4F7C-AD43-7B58BD24DBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9EDEED-4783-44FD-B107-83034B7731A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -51,9 +51,6 @@
     <t>AdditonalSubject</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -202,6 +199,9 @@
   </si>
   <si>
     <t>David Tickner</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -541,24 +541,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -581,153 +581,153 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="N2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R2" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB1" s="1" t="s">
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="U2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA2" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="R2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="U2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V2" t="s">
-        <v>49</v>
-      </c>
-      <c r="W2" t="s">
-        <v>50</v>
-      </c>
-      <c r="X2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="AB2" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -739,33 +739,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -777,19 +777,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8244481F-F1B5-4BC7-BE8A-260AA0DF5D37}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -800,16 +800,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB45B32-4FF3-421E-8C03-B189CD186655}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
+++ b/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9EDEED-4783-44FD-B107-83034B7731A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C49B091-119B-47A6-8055-319857C036E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
   <si>
     <t>Client</t>
   </si>
@@ -87,9 +87,6 @@
     <t>Staff</t>
   </si>
   <si>
-    <t>StdUser</t>
-  </si>
-  <si>
     <t>CaoUser</t>
   </si>
   <si>
@@ -123,9 +120,6 @@
     <t>HL Capital, Inc.</t>
   </si>
   <si>
-    <t>Rob Oudman</t>
-  </si>
-  <si>
     <t>Retainer</t>
   </si>
   <si>
@@ -189,9 +183,6 @@
     <t>Consulting</t>
   </si>
   <si>
-    <t>William Peluchiwski</t>
-  </si>
-  <si>
     <t>Gemma Hardy</t>
   </si>
   <si>
@@ -202,13 +193,19 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>James Craven</t>
+  </si>
+  <si>
+    <t>CF FinancialUser</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,13 +217,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -252,10 +242,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -601,61 +590,61 @@
       <c r="N1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="R1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="U1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="T1" s="3" t="s">
+      <c r="V1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -679,55 +668,55 @@
         <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="4" t="s">
+      <c r="N2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" t="s">
         <v>45</v>
       </c>
-      <c r="R2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" s="4" t="s">
+      <c r="V2" t="s">
         <v>46</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>47</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>48</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>49</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>50</v>
       </c>
-      <c r="Y2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>44</v>
+      <c r="AA2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -748,24 +737,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
         <v>53</v>
-      </c>
-      <c r="B2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -784,12 +773,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -804,12 +793,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
+++ b/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C49B091-119B-47A6-8055-319857C036E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9859EF6A-3C60-4697-A467-C21B275EC165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -192,13 +189,16 @@
     <t>David Tickner</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>James Craven</t>
   </si>
   <si>
     <t>CF FinancialUser</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
@@ -530,24 +530,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -558,165 +558,165 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="I2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="N2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB1" s="1" t="s">
+      <c r="S2" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="U2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W2" t="s">
+        <v>46</v>
+      </c>
+      <c r="X2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" t="s">
-        <v>22</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V2" t="s">
-        <v>46</v>
-      </c>
-      <c r="W2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="AB2" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -728,33 +728,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -766,19 +766,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8244481F-F1B5-4BC7-BE8A-260AA0DF5D37}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -789,16 +789,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB45B32-4FF3-421E-8C03-B189CD186655}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
+++ b/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9859EF6A-3C60-4697-A467-C21B275EC165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88778D1F-A548-4670-A45A-A86859C8A628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -198,7 +198,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -530,24 +530,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,7 +633,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -728,14 +728,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
@@ -746,7 +746,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -766,17 +766,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8244481F-F1B5-4BC7-BE8A-260AA0DF5D37}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -789,14 +789,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB45B32-4FF3-421E-8C03-B189CD186655}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>

--- a/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
+++ b/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8E92B7-D98F-4B7D-935F-57591DB304E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39034EB-A9C8-47F4-B62A-186DBDBFA304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -198,7 +198,7 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Brian Miller</t>
+    <t>Jennie Stewart</t>
   </si>
 </sst>
 </file>
@@ -530,24 +530,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,7 +633,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -728,14 +728,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -746,7 +746,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -766,17 +766,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8244481F-F1B5-4BC7-BE8A-260AA0DF5D37}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -789,14 +789,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB45B32-4FF3-421E-8C03-B189CD186655}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>26</v>
       </c>

--- a/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
+++ b/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39034EB-A9C8-47F4-B62A-186DBDBFA304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0FCF8A-8867-4B53-8978-AE19D43414ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" r:id="rId2"/>
+    <sheet name="Users" sheetId="2" r:id="rId1"/>
+    <sheet name="AddOpportunity" sheetId="1" r:id="rId2"/>
     <sheet name="AppName" sheetId="7" r:id="rId3"/>
     <sheet name="ModuleName" sheetId="8" r:id="rId4"/>
   </sheets>
@@ -528,26 +528,64 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,7 +671,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -725,58 +763,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8244481F-F1B5-4BC7-BE8A-260AA0DF5D37}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -789,14 +789,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB45B32-4FF3-421E-8C03-B189CD186655}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>

--- a/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
+++ b/TestData/LV_T1697AndT1698DNDOnOffEnableAndDisableMode.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0FCF8A-8867-4B53-8978-AE19D43414ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07B5468-790E-4D1A-B182-137D0488C63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId2"/>
-    <sheet name="AppName" sheetId="7" r:id="rId3"/>
-    <sheet name="ModuleName" sheetId="8" r:id="rId4"/>
+    <sheet name="OppJobTypes" sheetId="9" r:id="rId3"/>
+    <sheet name="AppName" sheetId="7" r:id="rId4"/>
+    <sheet name="ModuleName" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="62">
   <si>
     <t>Client</t>
   </si>
@@ -199,6 +200,21 @@
   </si>
   <si>
     <t>Jennie Stewart</t>
+  </si>
+  <si>
+    <t>Directs</t>
+  </si>
+  <si>
+    <t>Primary Capital Advisory</t>
+  </si>
+  <si>
+    <t>GP Stake Sale</t>
+  </si>
+  <si>
+    <t>LP-Led Secondaries</t>
+  </si>
+  <si>
+    <t>JobTypes</t>
   </si>
 </sst>
 </file>
@@ -533,8 +549,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -567,10 +583,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -757,6 +774,350 @@
         <v>41</v>
       </c>
     </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="U3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>46</v>
+      </c>
+      <c r="X3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R4" t="s">
+        <v>21</v>
+      </c>
+      <c r="S4" t="s">
+        <v>21</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="U4" t="s">
+        <v>44</v>
+      </c>
+      <c r="V4" t="s">
+        <v>45</v>
+      </c>
+      <c r="W4" t="s">
+        <v>46</v>
+      </c>
+      <c r="X4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S5" t="s">
+        <v>21</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="U5" t="s">
+        <v>44</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>46</v>
+      </c>
+      <c r="X5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R6" t="s">
+        <v>21</v>
+      </c>
+      <c r="S6" t="s">
+        <v>21</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="U6" t="s">
+        <v>44</v>
+      </c>
+      <c r="V6" t="s">
+        <v>45</v>
+      </c>
+      <c r="W6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -764,6 +1125,49 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76E73D3C-2745-4491-BE01-6837E8FCBC0E}">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8244481F-F1B5-4BC7-BE8A-260AA0DF5D37}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -786,10 +1190,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB45B32-4FF3-421E-8C03-B189CD186655}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
